--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9994-2021 artfynd.xlsx
+++ b/artfynd/A 9994-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129038541</v>
       </c>
       <c r="B2" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
